--- a/Dados/AJPS PSQ EXPERIMENT.xlsx
+++ b/Dados/AJPS PSQ EXPERIMENT.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/66dbe330cb88da91/Doutorado/Tese/Dados/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/66dbe330cb88da91/Doutorado/TeseDoutorado/Dados/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="116" documentId="11_B99231273C696DD00806BDAABBBE18832A9CF2B1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7BF82821-5F24-47E1-9900-CA051108F4A2}"/>
+  <xr:revisionPtr revIDLastSave="117" documentId="11_B99231273C696DD00806BDAABBBE18832A9CF2B1" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17D39680-97EB-49A5-A08F-6711BF345594}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4594,6 +4594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:E398"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
@@ -4614,7 +4615,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -4631,7 +4632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -4648,7 +4649,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>12</v>
       </c>
@@ -4665,7 +4666,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -4682,7 +4683,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>20</v>
       </c>
@@ -4699,7 +4700,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>24</v>
       </c>
@@ -4716,7 +4717,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>28</v>
       </c>
@@ -4750,7 +4751,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>36</v>
       </c>
@@ -4767,7 +4768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>40</v>
       </c>
@@ -4784,7 +4785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>44</v>
       </c>
@@ -4801,7 +4802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>48</v>
       </c>
@@ -4818,7 +4819,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>52</v>
       </c>
@@ -4835,7 +4836,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>56</v>
       </c>
@@ -4852,7 +4853,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>60</v>
       </c>
@@ -4869,7 +4870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>64</v>
       </c>
@@ -4886,7 +4887,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>68</v>
       </c>
@@ -4903,7 +4904,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>72</v>
       </c>
@@ -4920,7 +4921,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>76</v>
       </c>
@@ -4937,7 +4938,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>80</v>
       </c>
@@ -4954,7 +4955,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>84</v>
       </c>
@@ -4988,7 +4989,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>92</v>
       </c>
@@ -5005,7 +5006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>96</v>
       </c>
@@ -5022,7 +5023,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>100</v>
       </c>
@@ -5039,7 +5040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>104</v>
       </c>
@@ -5056,7 +5057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>108</v>
       </c>
@@ -5090,7 +5091,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>116</v>
       </c>
@@ -5107,7 +5108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>120</v>
       </c>
@@ -5124,7 +5125,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>124</v>
       </c>
@@ -5141,7 +5142,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>127</v>
       </c>
@@ -5158,7 +5159,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>131</v>
       </c>
@@ -5175,7 +5176,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>135</v>
       </c>
@@ -5192,7 +5193,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>139</v>
       </c>
@@ -5209,7 +5210,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>143</v>
       </c>
@@ -5226,7 +5227,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>146</v>
       </c>
@@ -5243,7 +5244,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>150</v>
       </c>
@@ -5260,7 +5261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>154</v>
       </c>
@@ -5277,7 +5278,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>158</v>
       </c>
@@ -5294,7 +5295,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>162</v>
       </c>
@@ -5328,7 +5329,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>169</v>
       </c>
@@ -5362,7 +5363,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>176</v>
       </c>
@@ -5379,7 +5380,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>180</v>
       </c>
@@ -5396,7 +5397,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>184</v>
       </c>
@@ -5447,7 +5448,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>196</v>
       </c>
@@ -5498,7 +5499,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>208</v>
       </c>
@@ -5515,7 +5516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>211</v>
       </c>
@@ -5532,7 +5533,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>215</v>
       </c>
@@ -5549,7 +5550,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>219</v>
       </c>
@@ -5583,7 +5584,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>226</v>
       </c>
@@ -5600,7 +5601,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>230</v>
       </c>
@@ -5617,7 +5618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>234</v>
       </c>
@@ -5634,7 +5635,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>238</v>
       </c>
@@ -5651,7 +5652,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>242</v>
       </c>
@@ -5668,7 +5669,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>246</v>
       </c>
@@ -5685,7 +5686,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>250</v>
       </c>
@@ -5702,7 +5703,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>254</v>
       </c>
@@ -5719,7 +5720,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>258</v>
       </c>
@@ -5736,7 +5737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>261</v>
       </c>
@@ -5753,7 +5754,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>265</v>
       </c>
@@ -5770,7 +5771,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>269</v>
       </c>
@@ -5787,7 +5788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>273</v>
       </c>
@@ -5804,7 +5805,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>277</v>
       </c>
@@ -5855,7 +5856,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>289</v>
       </c>
@@ -5872,7 +5873,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>293</v>
       </c>
@@ -5906,7 +5907,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>301</v>
       </c>
@@ -5940,7 +5941,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>309</v>
       </c>
@@ -5957,7 +5958,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>313</v>
       </c>
@@ -5974,7 +5975,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>317</v>
       </c>
@@ -5991,7 +5992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>321</v>
       </c>
@@ -6008,7 +6009,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>325</v>
       </c>
@@ -6025,7 +6026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>329</v>
       </c>
@@ -6042,7 +6043,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>333</v>
       </c>
@@ -6059,7 +6060,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>337</v>
       </c>
@@ -6093,7 +6094,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>345</v>
       </c>
@@ -6110,7 +6111,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>349</v>
       </c>
@@ -6127,7 +6128,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>353</v>
       </c>
@@ -6178,7 +6179,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>365</v>
       </c>
@@ -6212,7 +6213,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>373</v>
       </c>
@@ -6229,7 +6230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>377</v>
       </c>
@@ -6246,7 +6247,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>381</v>
       </c>
@@ -6263,7 +6264,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>385</v>
       </c>
@@ -6280,7 +6281,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>389</v>
       </c>
@@ -6297,7 +6298,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>392</v>
       </c>
@@ -6314,7 +6315,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>396</v>
       </c>
@@ -6331,7 +6332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>400</v>
       </c>
@@ -6348,7 +6349,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>404</v>
       </c>
@@ -6365,7 +6366,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>408</v>
       </c>
@@ -6382,7 +6383,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>412</v>
       </c>
@@ -6399,7 +6400,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>416</v>
       </c>
@@ -6416,7 +6417,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>420</v>
       </c>
@@ -6433,7 +6434,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>424</v>
       </c>
@@ -6450,7 +6451,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>428</v>
       </c>
@@ -6484,7 +6485,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>436</v>
       </c>
@@ -6501,7 +6502,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>440</v>
       </c>
@@ -6518,7 +6519,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>444</v>
       </c>
@@ -6535,7 +6536,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>448</v>
       </c>
@@ -6552,7 +6553,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>452</v>
       </c>
@@ -6586,7 +6587,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>460</v>
       </c>
@@ -6603,7 +6604,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>464</v>
       </c>
@@ -6620,7 +6621,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>468</v>
       </c>
@@ -6637,7 +6638,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>472</v>
       </c>
@@ -6654,7 +6655,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>476</v>
       </c>
@@ -6671,7 +6672,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>480</v>
       </c>
@@ -6688,7 +6689,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>484</v>
       </c>
@@ -6705,7 +6706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>487</v>
       </c>
@@ -6722,7 +6723,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>491</v>
       </c>
@@ -6739,7 +6740,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>495</v>
       </c>
@@ -6790,7 +6791,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>507</v>
       </c>
@@ -6807,7 +6808,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>511</v>
       </c>
@@ -6824,7 +6825,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>515</v>
       </c>
@@ -6841,7 +6842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>519</v>
       </c>
@@ -6858,7 +6859,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>523</v>
       </c>
@@ -6875,7 +6876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>527</v>
       </c>
@@ -6892,7 +6893,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>531</v>
       </c>
@@ -6909,7 +6910,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>535</v>
       </c>
@@ -6960,7 +6961,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>547</v>
       </c>
@@ -6977,7 +6978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>551</v>
       </c>
@@ -7011,7 +7012,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>559</v>
       </c>
@@ -7028,7 +7029,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>563</v>
       </c>
@@ -7045,7 +7046,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>567</v>
       </c>
@@ -7062,7 +7063,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>571</v>
       </c>
@@ -7079,7 +7080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>575</v>
       </c>
@@ -7096,7 +7097,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>579</v>
       </c>
@@ -7113,7 +7114,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>581</v>
       </c>
@@ -7147,7 +7148,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>587</v>
       </c>
@@ -7164,7 +7165,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>591</v>
       </c>
@@ -7181,7 +7182,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>595</v>
       </c>
@@ -7198,7 +7199,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>599</v>
       </c>
@@ -7215,7 +7216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>603</v>
       </c>
@@ -7232,7 +7233,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>607</v>
       </c>
@@ -7266,7 +7267,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>615</v>
       </c>
@@ -7283,7 +7284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>619</v>
       </c>
@@ -7300,7 +7301,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>623</v>
       </c>
@@ -7317,7 +7318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>627</v>
       </c>
@@ -7334,7 +7335,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>631</v>
       </c>
@@ -7351,7 +7352,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>635</v>
       </c>
@@ -7368,7 +7369,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>639</v>
       </c>
@@ -7385,7 +7386,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>643</v>
       </c>
@@ -7402,7 +7403,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>646</v>
       </c>
@@ -7419,7 +7420,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>650</v>
       </c>
@@ -7436,7 +7437,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>654</v>
       </c>
@@ -7470,7 +7471,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>662</v>
       </c>
@@ -7487,7 +7488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>666</v>
       </c>
@@ -7521,7 +7522,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>674</v>
       </c>
@@ -7538,7 +7539,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>678</v>
       </c>
@@ -7555,7 +7556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>682</v>
       </c>
@@ -7572,7 +7573,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>686</v>
       </c>
@@ -7589,7 +7590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>690</v>
       </c>
@@ -7606,7 +7607,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>694</v>
       </c>
@@ -7623,7 +7624,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>698</v>
       </c>
@@ -7640,7 +7641,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>702</v>
       </c>
@@ -7657,7 +7658,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>706</v>
       </c>
@@ -7674,7 +7675,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>710</v>
       </c>
@@ -7691,7 +7692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>714</v>
       </c>
@@ -7708,7 +7709,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>718</v>
       </c>
@@ -7725,7 +7726,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>722</v>
       </c>
@@ -7759,7 +7760,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>730</v>
       </c>
@@ -7776,7 +7777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>734</v>
       </c>
@@ -7793,7 +7794,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>737</v>
       </c>
@@ -7810,7 +7811,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>741</v>
       </c>
@@ -7827,7 +7828,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>745</v>
       </c>
@@ -7861,7 +7862,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>753</v>
       </c>
@@ -7878,7 +7879,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>757</v>
       </c>
@@ -7895,7 +7896,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>761</v>
       </c>
@@ -7912,7 +7913,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>765</v>
       </c>
@@ -7929,7 +7930,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>769</v>
       </c>
@@ -7946,7 +7947,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>773</v>
       </c>
@@ -7963,7 +7964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>777</v>
       </c>
@@ -8014,7 +8015,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>789</v>
       </c>
@@ -8048,7 +8049,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>797</v>
       </c>
@@ -8065,7 +8066,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>801</v>
       </c>
@@ -8082,7 +8083,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>805</v>
       </c>
@@ -8099,7 +8100,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>809</v>
       </c>
@@ -8116,7 +8117,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>813</v>
       </c>
@@ -8133,7 +8134,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>817</v>
       </c>
@@ -8150,7 +8151,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>821</v>
       </c>
@@ -8167,7 +8168,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>825</v>
       </c>
@@ -8184,7 +8185,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>829</v>
       </c>
@@ -8201,7 +8202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>833</v>
       </c>
@@ -8218,7 +8219,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>837</v>
       </c>
@@ -8235,7 +8236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>841</v>
       </c>
@@ -8252,7 +8253,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>845</v>
       </c>
@@ -8286,7 +8287,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>853</v>
       </c>
@@ -8320,7 +8321,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>861</v>
       </c>
@@ -8337,7 +8338,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>865</v>
       </c>
@@ -8354,7 +8355,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="222" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>869</v>
       </c>
@@ -8371,7 +8372,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="223" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>873</v>
       </c>
@@ -8388,7 +8389,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="224" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>877</v>
       </c>
@@ -8405,7 +8406,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>881</v>
       </c>
@@ -8456,7 +8457,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="228" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>893</v>
       </c>
@@ -8473,7 +8474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="229" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>897</v>
       </c>
@@ -8524,7 +8525,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="232" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>909</v>
       </c>
@@ -8541,7 +8542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="233" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>913</v>
       </c>
@@ -8558,7 +8559,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="234" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" t="s">
         <v>917</v>
       </c>
@@ -8575,7 +8576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" t="s">
         <v>921</v>
       </c>
@@ -8592,7 +8593,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" t="s">
         <v>925</v>
       </c>
@@ -8626,7 +8627,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="238" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" t="s">
         <v>933</v>
       </c>
@@ -8728,7 +8729,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="244" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" t="s">
         <v>957</v>
       </c>
@@ -8813,7 +8814,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="249" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" t="s">
         <v>977</v>
       </c>
@@ -8830,7 +8831,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" t="s">
         <v>981</v>
       </c>
@@ -8847,7 +8848,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>985</v>
       </c>
@@ -8881,7 +8882,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="253" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A253" t="s">
         <v>993</v>
       </c>
@@ -8898,7 +8899,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="254" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A254" t="s">
         <v>997</v>
       </c>
@@ -8915,7 +8916,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A255" t="s">
         <v>1001</v>
       </c>
@@ -8932,7 +8933,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A256" t="s">
         <v>1005</v>
       </c>
@@ -8966,7 +8967,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="258" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>1013</v>
       </c>
@@ -9000,7 +9001,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="260" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>1021</v>
       </c>
@@ -9017,7 +9018,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>1025</v>
       </c>
@@ -9051,7 +9052,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="263" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="263" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A263" t="s">
         <v>1033</v>
       </c>
@@ -9068,7 +9069,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A264" t="s">
         <v>1037</v>
       </c>
@@ -9085,7 +9086,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A265" t="s">
         <v>1041</v>
       </c>
@@ -9102,7 +9103,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>1045</v>
       </c>
@@ -9119,7 +9120,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>1049</v>
       </c>
@@ -9136,7 +9137,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>1053</v>
       </c>
@@ -9153,7 +9154,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="269" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>1057</v>
       </c>
@@ -9170,7 +9171,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>1061</v>
       </c>
@@ -9187,7 +9188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>1065</v>
       </c>
@@ -9204,7 +9205,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>1069</v>
       </c>
@@ -9221,7 +9222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="273" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>1073</v>
       </c>
@@ -9255,7 +9256,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="275" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>1081</v>
       </c>
@@ -9289,7 +9290,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="277" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>1089</v>
       </c>
@@ -9306,7 +9307,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="278" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="278" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>1093</v>
       </c>
@@ -9323,7 +9324,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A279" t="s">
         <v>1097</v>
       </c>
@@ -9340,7 +9341,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A280" t="s">
         <v>1101</v>
       </c>
@@ -9374,7 +9375,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="282" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A282" t="s">
         <v>1109</v>
       </c>
@@ -9391,7 +9392,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A283" t="s">
         <v>1113</v>
       </c>
@@ -9408,7 +9409,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A284" t="s">
         <v>1117</v>
       </c>
@@ -9425,7 +9426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A285" t="s">
         <v>1121</v>
       </c>
@@ -9442,7 +9443,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A286" t="s">
         <v>1125</v>
       </c>
@@ -9476,7 +9477,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="288" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A288" t="s">
         <v>1133</v>
       </c>
@@ -9493,7 +9494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A289" t="s">
         <v>1137</v>
       </c>
@@ -9510,7 +9511,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="290" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A290" t="s">
         <v>1141</v>
       </c>
@@ -9527,7 +9528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:5" ht="13.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" t="s">
         <v>1144</v>
       </c>
@@ -9544,7 +9545,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A292" t="s">
         <v>1148</v>
       </c>
@@ -9578,7 +9579,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="294" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A294" t="s">
         <v>1156</v>
       </c>
@@ -9595,7 +9596,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A295" t="s">
         <v>1160</v>
       </c>
@@ -9612,7 +9613,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A296" t="s">
         <v>1164</v>
       </c>
@@ -9646,7 +9647,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="298" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A298" t="s">
         <v>1172</v>
       </c>
@@ -9680,7 +9681,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="300" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A300" t="s">
         <v>1180</v>
       </c>
@@ -9697,7 +9698,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A301" t="s">
         <v>1184</v>
       </c>
@@ -9714,7 +9715,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A302" t="s">
         <v>1188</v>
       </c>
@@ -9731,7 +9732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="303" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A303" t="s">
         <v>1192</v>
       </c>
@@ -9748,7 +9749,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="304" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A304" t="s">
         <v>1196</v>
       </c>
@@ -9799,7 +9800,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="307" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A307" t="s">
         <v>1208</v>
       </c>
@@ -9816,7 +9817,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="308" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A308" t="s">
         <v>1212</v>
       </c>
@@ -9833,7 +9834,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="309" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A309" t="s">
         <v>1215</v>
       </c>
@@ -9850,7 +9851,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="310" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A310" t="s">
         <v>1219</v>
       </c>
@@ -9867,7 +9868,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="311" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A311" t="s">
         <v>1223</v>
       </c>
@@ -9884,7 +9885,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="312" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A312" t="s">
         <v>1227</v>
       </c>
@@ -9918,7 +9919,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="314" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A314" t="s">
         <v>1234</v>
       </c>
@@ -9935,7 +9936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="315" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A315" t="s">
         <v>1238</v>
       </c>
@@ -9966,7 +9967,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="317" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A317" t="s">
         <v>1243</v>
       </c>
@@ -9994,7 +9995,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="319" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A319" t="s">
         <v>1247</v>
       </c>
@@ -10064,7 +10065,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="324" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A324" t="s">
         <v>1257</v>
       </c>
@@ -10246,7 +10247,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="337" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A337" t="s">
         <v>1281</v>
       </c>
@@ -10260,7 +10261,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="338" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A338" t="s">
         <v>1283</v>
       </c>
@@ -10302,7 +10303,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="341" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A341" t="s">
         <v>1289</v>
       </c>
@@ -10358,7 +10359,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="345" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="345" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A345" t="s">
         <v>1297</v>
       </c>
@@ -10386,7 +10387,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="347" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="347" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A347" t="s">
         <v>1301</v>
       </c>
@@ -10498,7 +10499,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="355" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A355" t="s">
         <v>1317</v>
       </c>
@@ -10512,7 +10513,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="356" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="356" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A356" t="s">
         <v>1319</v>
       </c>
@@ -10540,7 +10541,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="358" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A358" t="s">
         <v>1323</v>
       </c>
@@ -10610,7 +10611,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="363" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A363" t="s">
         <v>1332</v>
       </c>
@@ -10680,7 +10681,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="368" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="368" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A368" t="s">
         <v>1342</v>
       </c>
@@ -10722,7 +10723,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="371" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="371" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A371" t="s">
         <v>1348</v>
       </c>
@@ -10736,7 +10737,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="372" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="372" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
         <v>1350</v>
       </c>
@@ -10834,7 +10835,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="379" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A379" t="s">
         <v>1364</v>
       </c>
@@ -10932,7 +10933,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="386" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="386" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A386" t="s">
         <v>1378</v>
       </c>
@@ -10988,7 +10989,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="390" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="390" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A390" t="s">
         <v>1386</v>
       </c>
@@ -11016,7 +11017,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="392" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="392" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
         <v>1390</v>
       </c>
@@ -11072,7 +11073,7 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="396" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="396" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A396" t="s">
         <v>1398</v>
       </c>
@@ -11115,7 +11116,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:E398" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:E398" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="4">
+      <filters>
+        <filter val="-1"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>
